--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/DICE/adaptive/entropy/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/DICE/adaptive/entropy/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -651,6 +651,80 @@
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>dice_p=50,ash_p=None,react_th=None,scale_th=10.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>90.33</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=5,ash_p=None,react_th=None,scale_th=5.0,type=entropy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>37.96</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>90.76000000000001</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>86.28</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>92.59</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>93.06999999999999</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=None,scale_th=5.0,type=entropy</t>
         </is>
       </c>
     </row>
